--- a/majExemples/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/majExemples/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T12:31:15+00:00</t>
+    <t>2026-10-05T16:04:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
